--- a/docs/화면목록_전체.xlsx
+++ b/docs/화면목록_전체.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="사용자 화면 전체" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="관리자 화면 전체" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -90,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -112,6 +113,30 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -510,17 +535,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>메인 홈페이지</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>메인 홈페이지</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/newhome</t>
         </is>
@@ -532,17 +557,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>메인 홈페이지</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>문항 미리보기</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/sample/questions</t>
         </is>
@@ -554,17 +579,17 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>메인 홈페이지</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>샘플 PDF 뷰어</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/sample/report</t>
         </is>
@@ -576,17 +601,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>메인 홈페이지</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>사람이 보는 분석 (HITL)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/about/hitl</t>
         </is>
@@ -598,17 +623,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>메인 홈페이지</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>자주 묻는 질문</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/support/faq</t>
         </is>
@@ -620,17 +645,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>학부모 홈</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my</t>
         </is>
@@ -642,17 +667,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>결과 리포트</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/result?student=mu6976f8-GFQTSQYZ</t>
         </is>
@@ -664,17 +689,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>학생 프로필</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/children</t>
         </is>
@@ -686,17 +711,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>학생 등록</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/children/new</t>
         </is>
@@ -708,17 +733,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>학생 상세</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/children/mu6976f8-GFQTSQYZ</t>
         </is>
@@ -730,17 +755,17 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>단계별 동의 관리</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/children/consent-stages</t>
         </is>
@@ -752,17 +777,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>동의 철회·데이터 파기 요청</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/children/withdraw</t>
         </is>
@@ -774,17 +799,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>학생 명부 (개별 등록)</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/students</t>
         </is>
@@ -796,17 +821,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>학생 일괄 등록</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/students?tab=bulk</t>
         </is>
@@ -818,17 +843,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>결제</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/payments</t>
         </is>
@@ -840,17 +865,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>설문 현황</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/surveys</t>
         </is>
@@ -862,17 +887,17 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>학생 설문 상세</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/surveys/mu6976f8-GFQTSQYZ</t>
         </is>
@@ -884,17 +909,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>면담</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/interviews</t>
         </is>
@@ -906,17 +931,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>마이페이지</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/mypage</t>
         </is>
@@ -928,17 +953,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>내 정보 설정</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/account</t>
         </is>
@@ -950,17 +975,17 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>알림 설정</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/account/notification</t>
         </is>
@@ -972,17 +997,17 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>회원 탈퇴</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/account/leave</t>
         </is>
@@ -994,17 +1019,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>소속 승인 대기</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/pending</t>
         </is>
@@ -1016,17 +1041,17 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>(구) 응시권 결제</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/payment</t>
         </is>
@@ -1038,17 +1063,17 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>학부모 대시보드</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>(구) 별도 동의 화면</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/children/consent</t>
         </is>
@@ -1060,17 +1085,17 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>학생 대시보드</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>학생 응시 로그인</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/login/student</t>
         </is>
@@ -1082,17 +1107,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>학생 대시보드</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>학생 홈</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/student</t>
         </is>
@@ -1104,17 +1129,17 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>학생 대시보드</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>평가 보기</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/student/exams</t>
         </is>
@@ -1126,17 +1151,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>학생 대시보드</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>응시 결과</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/student/results</t>
         </is>
@@ -1148,17 +1173,17 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>학생 대시보드</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>내 설문</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/student/surveys</t>
         </is>
@@ -1170,17 +1195,17 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>학생 대시보드</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>내 정보</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/student/account</t>
         </is>
@@ -1192,17 +1217,17 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>학생 대시보드</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>결제 (만 14세 이상)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/student/payments</t>
         </is>
@@ -1214,17 +1239,17 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>학생 대시보드</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>면담 (만 14세 이상)</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/student/interviews</t>
         </is>
@@ -1236,17 +1261,17 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>평가 — 비회원</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>평가 목록 (셋트 모드)</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam</t>
         </is>
@@ -1258,17 +1283,17 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>평가 — 비회원</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>셋트 문항 (무료 체험)</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/session/trial/2026-3/e34</t>
         </is>
@@ -1280,17 +1305,17 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>평가 — 비회원</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>접수하기 (평가 둘러보기)</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/apply</t>
         </is>
@@ -1302,17 +1327,17 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>평가 — 비회원</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>시험 안내</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/info</t>
         </is>
@@ -1324,17 +1349,17 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>평가 — 비회원</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>서비스 안내</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/guide</t>
         </is>
@@ -1346,17 +1371,17 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>평가 — 비회원</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>문항 미리보기</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/sample/questions</t>
         </is>
@@ -1368,17 +1393,17 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>평가 — 비회원</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>샘플 PDF 뷰어</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/sample/report</t>
         </is>
@@ -1390,17 +1415,17 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>평가 — 비회원</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>대시보드 데모</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/sample/demo</t>
         </is>
@@ -1412,17 +1437,17 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>가입·로그인 (비회원→회원)</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>회원가입</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/signup</t>
         </is>
@@ -1434,17 +1459,17 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>가입·로그인 (비회원→회원)</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>회원 유형 선택</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/signup/type</t>
         </is>
@@ -1456,17 +1481,17 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>가입·로그인 (비회원→회원)</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>회원가입 · 정보 입력</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/signup/join</t>
         </is>
@@ -1478,17 +1503,17 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>가입·로그인 (비회원→회원)</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>법정대리인 동의 요청</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/signup/guardian</t>
         </is>
@@ -1500,17 +1525,17 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>가입·로그인 (비회원→회원)</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>법정대리인 동의</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/consent/guardian</t>
         </is>
@@ -1522,17 +1547,17 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>가입·로그인 (비회원→회원)</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>가입 완료</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/signup/done</t>
         </is>
@@ -1544,17 +1569,17 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>가입·로그인 (비회원→회원)</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>기관·평가코드 연결</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/signup/link</t>
         </is>
@@ -1566,17 +1591,17 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>가입·로그인 (비회원→회원)</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>로그인</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/login</t>
         </is>
@@ -1588,17 +1613,17 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>가입·로그인 (비회원→회원)</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>계정 찾기</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/login/recover</t>
         </is>
@@ -1610,17 +1635,17 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>평가 — 회원(무료)</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>응시하기</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam</t>
         </is>
@@ -1632,17 +1657,17 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>평가 — 회원(무료)</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>무료시험 응시</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/session/free</t>
         </is>
@@ -1654,17 +1679,17 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>평가 — 회원(무료)</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>평가 보기 (학생 레일)</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/student/exams</t>
         </is>
@@ -1676,17 +1701,17 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>평가 — 회원(무료)</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>결과보기</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/report</t>
         </is>
@@ -1698,17 +1723,17 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>평가 — 회원(무료)</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>진단 보고서 · 요약본</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/report/summary</t>
         </is>
@@ -1720,17 +1745,17 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>접수하기</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/apply</t>
         </is>
@@ -1742,17 +1767,17 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>결제 (보호자)</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/payments</t>
         </is>
@@ -1764,17 +1789,17 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>결제 (학생, 만 14세 이상)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/student/payments</t>
         </is>
@@ -1786,17 +1811,17 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>과목 응시 현황</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/2026-3/e34</t>
         </is>
@@ -1808,17 +1833,17 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>유료시험 응시 (과목별)</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/session/paid/science</t>
         </is>
@@ -1830,17 +1855,17 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>(구) 응시 주소</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/session/science</t>
         </is>
@@ -1852,17 +1877,17 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>정답과 해설</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/answers</t>
         </is>
@@ -1874,17 +1899,17 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>결과보기</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/report</t>
         </is>
@@ -1896,17 +1921,17 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>결과 리포트</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/exam/result</t>
         </is>
@@ -1918,17 +1943,17 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="9" t="inlineStr">
         <is>
           <t>진단 보고서 · 정밀본</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/report/full</t>
         </is>
@@ -1940,17 +1965,17 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>면담 (보호자)</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/interviews</t>
         </is>
@@ -1962,17 +1987,17 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>평가 — 회원(유료)</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>면담 (학생, 만 14세 이상)</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/student/interviews</t>
         </is>
@@ -1984,17 +2009,17 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>설문 화면</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>설문 현황 (보호자·기관)</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/surveys</t>
         </is>
@@ -2006,17 +2031,17 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>설문 화면</t>
         </is>
       </c>
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>학생 설문 상세</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my/surveys/mu6976f8-GFQTSQYZ</t>
         </is>
@@ -2028,17 +2053,17 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="10" t="inlineStr">
         <is>
           <t>설문 화면</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>내 설문 (학생)</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C71" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/student/surveys</t>
         </is>
@@ -2050,17 +2075,17 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>설문 화면</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>학생 재능진단 설문지</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C72" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/survey/student?student=mu6976f8-GFQTSQYZ</t>
         </is>
@@ -2072,17 +2097,17 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>설문 화면</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>학부모 재능진단 설문지</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C73" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/survey/guardian?student=mu6976f8-GFQTSQYZ</t>
         </is>
@@ -2094,17 +2119,17 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>설문 화면</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>지도교사 관찰 설문</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C74" s="11" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/survey/teacher?student=mu6976f8-GFQTSQYZ</t>
         </is>
@@ -2116,17 +2141,17 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>참고 · 시안</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>학부모 홈 시안 1 / 2</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/my1</t>
         </is>
@@ -2138,17 +2163,17 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>참고 · 시안</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>마이페이지 시안 1 / 2</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>https://genixx-theta.vercel.app/mypage1</t>
         </is>
@@ -2156,6 +2181,1236 @@
       <c r="D76" s="4" t="inlineStr">
         <is>
           <t>MyPage variant 1(전문가) · 2(둥글둥글) (/mypage1 · /mypage2). 검토용 디자인 시안.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>화면명</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ADM-01. 지표가 아니라 「오늘 처리할 큐」부터 보여 준다. 기둥(왼쪽 메뉴)의 배지와 「내 앞에 쌓인 것」이 같은 값을 쓴다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>운영</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>판정 큐</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/queue</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>EXP-07. AI 1차 제안값을 사람이 확정하는 자리 — 이 콘솔의 중심. 아직 확정되지 않은 건(AI·검토·협진)이 배지로 선다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/members</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>ADM-02. 회원 명부. 연락처는 가려서 표시한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>회원 상세</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/members/[id]</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>회원 한 사람의 가입 정보·동의·자녀·결제 이력.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>학생·접속코드</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/students</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>ADM-02-1. 학생 명부와 접속코드. 이름·생년월일은 기본 가림이고, 사유를 적어야 그 줄만 열린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>학생 상세</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/students/[id]</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>학생 한 명의 등록 정보·접속코드·응시 이력.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/orgs</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>ORG-02. 기관 계약과 응시권 배정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>기관 상세</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/orgs/[id]</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>기관 하나의 계약·구성원·배정 현황.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>가입 승인</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/approvals</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>ADM-02-2. 교사·기관담당자 가입 신청을 받는 자리(/my/pending의 반대편). 처리한 신청은 브라우저 저장소에만 남아 배지를 화면에서 센다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>가입 신청 상세</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/approvals/[id]</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>신청 한 건을 펴서 승인·반려한다. 예: /admin2/approvals/AP-2608-031</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>개인정보 관리</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/privacy</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>ADM-10. 「이 회원이 무엇에 동의했나」를 보는 자리. 회원을 보다가 드는 물음이라 명부 옆에 둔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>개인정보 상세</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/privacy/[id]</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>한 사람의 동의 이력과 열람 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>회원</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>파기 스케줄러</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/privacy/purge</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>ADM-10-1. 파기 대상과 일정. 명부에서 일부러 떼어 둔다 — 매일 훑는 화면 안에 되돌릴 수 없는 단추를 두지 않기 위해서다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>문항관리</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>문항 출제</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/authoring</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>EXP-02. 「무엇부터 여나」만 답하는 목록 — 작성 중과 반려됨이 선다. 실제로 채우는 일은 문항 상세에서 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>문항관리</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>문항 검수</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/review</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>EXP-03. 검수 대기 목록. 기둥에 세운 까닭은 「지금 검수할 게 몇 개인가」를 은행에 들어가 거르개를 걸어야 알 수 있었기 때문이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>문항관리</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>문항 은행</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/items</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ADM-04. 승인되어 쌓인 문항. 상태·과목·학년으로 거른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>문항관리</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>문항 상세</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/items/[id]</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>고치는 자리는 여기 하나다 — 출제·검수 화면은 무엇부터 열지만 답한다. 예: /admin2/items/IT-2601</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>평가 관리</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>평가 회차</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/rounds</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>ADM-05. 언제 여는가 · 어떤 학년과 과목을 보는가. 회차 진행률과 응시·포기 현황.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>평가 관리</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>회차 생성</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/rounds/new</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>새 회차를 연다. 학년과 과목은 회차마다 정하는 값이라 여기서 고른다(PlanPicker).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>평가 관리</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>회차 편성</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/rounds/[id]</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>ADM-05-4. 회차 하나의 기간·정원·값과 회차 공지·유의사항. 예: /admin2/rounds/2026-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>평가 관리</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>평가별 문항관리</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/forms</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>ADM-04-3. 회차마다 과목별 검사지가 어디까지 짜였는가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>평가 관리</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>회차 문항 편성</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/forms/[round]</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>그 회차의 검사지에 문항을 담는 자리. 과목별 재고가 고르는 자리 바로 옆에 선다. 예: /admin2/forms/2026-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>채점 관리</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>평가 채점</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/grading</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>EXP-04. 「지금 봐야 하는 응답이 무엇인가」 — 단위가 「응답」이라 확신도가 낮은 것부터 훑는다. AI 채점 검토와 루브릭 채점이 한 화면이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>채점 관리</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>채점대</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/grading/[id]</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>응답 하나를 펴서 배점과 근거를 적는 자리. 예: /admin2/grading/SC-…</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>채점 관리</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>회원 채점</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/grading/members</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>EXP-04-1. 「이 아이에게 무엇을 돌려주는가」 — 단위가 「사람」이라 답안지를 통째로 펴 놓고 배점을 손보고 해설을 붙인다. 자료는 평가 채점과 한 벌이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>채점 관리</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>답안지</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/grading/members/[key]</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>학생 한 명의 답안지 전체. 여기서 고친 배점이 평가 채점 목록에 그대로 선다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>면담 관리</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>면담 신청</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/interviews</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>EXP-06. 「누구부터 잡나」 — 단위가 케이스라 상태와 대기 일수로 세운다. 대기 건수가 배지로 선다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>면담 관리</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>면담 상세</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/interviews/[id]</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>면담 한 건의 신청 내용·일정·기록. 판정의 근거 문자열이 이 번호를 itv=…로 가리킨다. 예: /admin2/interviews/IV-2603-0423</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>면담 관리</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>면담 일정</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/interviews/calendar</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>EXP-06-1. 「어느 날이 비었나」 — 단위가 날짜라 달력으로 편다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>면담 관리</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>상담사 관리</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/counselors</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>EXP-06-2. 면담을 맡는 사람. 근무 요일과 맡는 물음, 「이 사람의 30분」 값을 한 화면에서 정한다 — 그래서 상품 목록이 아니라 여기에 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>면담 관리</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>상담사 상세</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/counselors/[id]</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>상담사 한 사람의 일정·단가·배정 현황.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>리포트 관리</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>리포트 승인</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/reports/approval</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>EXP-08. 확정된 판정을 리포트로 내보내는 자리. 이 그룹에서 매일 여는 것은 이 화면이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>리포트 관리</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>리포트 상세</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/reports/approval/[id]</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>리포트 한 장을 펴서 문구를 확인하고 발행한다. 문구가 이상하면 곧바로 해석 템플릿으로 간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>리포트 관리</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>해석 템플릿</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/reports/templates</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>ADM-08-1. 아이에게 나가는 「글」을 쓴다. 단위가 문장이고 학년대마다 다르다. 활동 제안도 이 안의 한 자리(slot: activity)로 들어가 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>리포트 관리</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>해석 템플릿 상세</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/reports/templates/[id]</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>템플릿 한 벌의 문장을 고친다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>리포트 관리</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>조립 규칙</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/reports/rules</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>ADM-08-4. 그 글을 「언제 부를지」를 정한다. 단위가 조건이고 학년과 무관하다. 잘못 건드리면 리포트가 통째로 달라지는 값이라 템플릿과 화면을 갈라 두었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/notices</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>ADM-15. 사이트 공지 — 회차 모집·점검 안내. (회차마다 붙는 공지·유의사항은 회차 편성에서 고친다.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>공지 상세</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/notices/[id]</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>공지 한 건을 쓰고 고친다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>자주 묻는 질문</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/faq</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>ADM-15-1. 고객지원(/support/faq)과 홈이 읽는 목록. 여태 화면 파일에 박혀 있어 운영자가 손댈 수 없던 글을 여기로 들였다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>자주 묻는 질문 상세</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/faq/[id]</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>문답 한 건을 쓰고 고친다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>홍보 영상</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/clips</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>ADM-15-2. 첫 화면에 걸리는 영상. 적는 것이 글이 아니라 유튜브 주소일 뿐, 고치러 오는 사람은 공지·FAQ와 같은 사람이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>홍보 영상 상세</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/clips/[id]</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>영상 한 건의 주소와 문구.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>문의</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/inquiries</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>ADM-10. 1:1 문의와 기관 도입 문의. 답하지 않은 건이 배지로 선다. 자주 묻는 질문 바로 아래에 둔 까닭은 답을 쓰다가 「아예 올려 두자」로 이어지기 때문이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>콘텐츠</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>문의 상세</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/inquiries/[id]</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>문의 한 건에 답한다. 예: /admin2/inquiries/IQ-26080912</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>결제 관리</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>상품 관리</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/products</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>PAY-01. 무엇을 얼마에 파는가 — 등록하고 고치는 자리. 여기서 정한 값을 접수·결제 화면이 그대로 읽는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>결제 관리</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>상품 등록</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/products/new</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>새 상품을 등록한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>결제 관리</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>상품 수정</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/products/[id]</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>상품 하나의 값과 조건을 고친다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>결제 관리</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>결제 내역</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/payments</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>PAY-02. 그래서 얼마가 들어왔는가 — 「읽기만 한다」. 승인·취소·환불은 결제대행사에서 일어나고 여기로는 결과만 넘어온다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>운영자·권한</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/staff</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>ADM-03. 운영자 계정과 역할별 권한 표.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>운영자 상세</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/staff/[id]</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>운영자 한 사람의 역할과 권한.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>감사 로그</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/audit</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>ADM-11. 개인정보 열람 기록. 가림을 연 건은 전건이 여기로 쌓인다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>시스템 설정</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/settings</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>ADM-13. 지금 걸려 있는 값을 읽는 자리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>AI 프롬프트</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/ai</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>ADM-13-1. 시스템 설정 가운데 운영자가 실제로 손댈 수 있는 한 갈래. 프롬프트 하나가 출제·채점·판정에 걸쳐 있어 어느 업무 그룹에도 넣지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>시스템</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>AI 프롬프트 상세</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>https://genixx-theta.vercel.app/admin2/ai/[id]</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>프롬프트 한 벌을 고치고 판을 남긴다.</t>
         </is>
       </c>
     </row>
